--- a/xlsx/換色紀錄表(11).xlsx
+++ b/xlsx/換色紀錄表(11).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d310cb6cf3413c87/換色紀錄表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="848" documentId="11_4FBE7C339D0C5806B5E87E471C75590E52E680CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{220A568C-4BA9-2A47-9845-2CA555D199AE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{14540C4E-D695-7E45-9987-450498D36951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-104" yWindow="-104" windowWidth="29699" windowHeight="12050" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-104" yWindow="-104" windowWidth="29699" windowHeight="12050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="每日用粉紀錄表" sheetId="1" r:id="rId1"/>
@@ -2009,16 +2009,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2028,9 +2018,12 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2048,6 +2041,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="E2" s="29">
         <f ca="1">TODAY()</f>
-        <v>45264</v>
+        <v>46300</v>
       </c>
       <c r="F2" s="130" t="str">
         <f ca="1">TEXT(WEEKDAY(E2,1),"aaaa")</f>
@@ -11122,20 +11122,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1:L1048576">
-    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="例假日">
+    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="年假">
+      <formula>NOT(ISERROR(SEARCH("年假",L1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="17" priority="2" operator="containsText" text="例假日">
       <formula>NOT(ISERROR(SEARCH("例假日",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="颱風假">
+    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="颱風假">
       <formula>NOT(ISERROR(SEARCH("颱風假",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="年假">
-      <formula>NOT(ISERROR(SEARCH("年假",L1)))</formula>
+    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="無烤漆">
+      <formula>NOT(ISERROR(SEARCH("無烤漆",L1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="6" operator="containsText" text="國定假日">
+    <cfRule type="containsText" dxfId="14" priority="6" operator="containsText" text="國定假日">
       <formula>NOT(ISERROR(SEARCH("國定假日",L1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="4" operator="containsText" text="無烤漆">
-      <formula>NOT(ISERROR(SEARCH("無烤漆",L1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4:M291">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="G2" s="29">
         <f ca="1">TODAY()</f>
-        <v>45264</v>
+        <v>46300</v>
       </c>
       <c r="H2" s="73" t="str">
         <f ca="1">TEXT(WEEKDAY(每日用粉紀錄表!E2,1),"aaaa")</f>
